--- a/Automobile_Sector_Projects/Car_Sales_Analysis/CarSalesByModelEnd.xlsx
+++ b/Automobile_Sector_Projects/Car_Sales_Analysis/CarSalesByModelEnd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Automobile_Sector_Projects\Car_Sales_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AC3676-CC51-4B0F-8200-35C8C1471755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FED8EB-7580-47B2-B81F-5EE7A1251EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6882,8 +6882,8 @@
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>220980</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
@@ -6901,7 +6901,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="419100" y="266700"/>
-          <a:ext cx="12603480" cy="3436620"/>
+          <a:ext cx="10355580" cy="3436620"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6953,91 +6953,229 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Navigation in Excel</a:t>
+            <a:t>. Navigation in Excel - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>NAVIGATION</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Selecting the data in Excel</a:t>
+            <a:t>. Selecting the data in Excel - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SELECTION</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Viewing the data in Excel </a:t>
+            <a:t>. Viewing the data in Excel- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>VIEWING</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Enter/Edit data in worksheet in Excel</a:t>
+            <a:t>. Enter/Edit data in worksheet in Excel - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>EDITING/ENTERING</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Move/Copy/Paste data in worksheet in Excel</a:t>
+            <a:t>. Move/Copy/Paste data in worksheet in Excel - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>MOVE/COPY/PASTE</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Fill data in worksheet in excel</a:t>
+            <a:t>. Fill data in worksheet in excel - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FILL DATA</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Format data/cells in worksheet in Excel</a:t>
+            <a:t>. Format data/cells in worksheet in Excel - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FORMAT</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Formulae in excel - Basic, selecting ranges in formulae, copy formulas</a:t>
+            <a:t>. Formulae in excel - Basic, selecting ranges in formulae, copy formulas -</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FORMULAE</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Refrences in excel - Relative, Absolute, Mixed Refrences</a:t>
+            <a:t>. Refrences in excel - Relative, Absolute, Mixed Refrences- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>REFRENCES</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Errors in excel</a:t>
+            <a:t>. Errors in excel - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>ERRORS</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Importing data in excel (CSV) </a:t>
+            <a:t>. Importing data in excel (CSV)- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>IMPORTING DATA</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Removing Duplicate, Inaccurate, Spelling errors, extra white spaces, wrong case, missing values, date formatting errors and Empty Rows/Columns</a:t>
+            <a:t>. Removing Duplicate, Inaccurate, Spelling errors, extra white spaces, wrong case, missing values, date formatting errors and Empty Rows/Columns - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>REMOVE INCONSISTENCIES</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Flash Fill &amp; Text to Columns for Data cleaning</a:t>
+            <a:t>. Flash Fill &amp; Text to Columns for Data cleaning - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FLASH FILL, TEXT TO COLUMNS</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Filtering &amp; Sorting the data</a:t>
+            <a:t>. Filtering &amp; Sorting the data - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FILTER &amp; SORT</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. Function for data Analysis IF, IFS, COUNTIF, COUNTIFS, SUMIF, SUMIFS, HLOOKUP, VLOOKUP, XLOOKUP, INDEX, MATCH</a:t>
+            <a:t>. Function for data Analysis IF, IFS, COUNTIF, COUNTIFS, SUMIF, SUMIFS, HLOOKUP, VLOOKUP, XLOOKUP, INDEX, MATCH- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>FUNCTIONS</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>. What if analysis in excel - </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>WHAT IF ANALYSIS</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -19336,7 +19474,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="1">
-        <v>43101.958333333343</v>
+        <v>43101.958333333336</v>
       </c>
       <c r="E17">
         <v>1301</v>

--- a/Automobile_Sector_Projects/Car_Sales_Analysis/CarSalesByModelEnd.xlsx
+++ b/Automobile_Sector_Projects/Car_Sales_Analysis/CarSalesByModelEnd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Automobile_Sector_Projects\Car_Sales_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FED8EB-7580-47B2-B81F-5EE7A1251EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EB4D73-DBC1-4820-B41F-6C9623BAB1F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CarSales" sheetId="2" r:id="rId1"/>
@@ -6961,7 +6961,7 @@
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>NAVIGATION</a:t>
+            <a:t>NAVIGATION - 10</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -6975,7 +6975,7 @@
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>SELECTION</a:t>
+            <a:t>SELECTION - (10 + 3 + </a:t>
           </a:r>
         </a:p>
         <a:p>

--- a/Automobile_Sector_Projects/Car_Sales_Analysis/CarSalesByModelEnd.xlsx
+++ b/Automobile_Sector_Projects/Car_Sales_Analysis/CarSalesByModelEnd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Automobile_Sector_Projects\Car_Sales_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EB4D73-DBC1-4820-B41F-6C9623BAB1F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73755A83-CAE4-41A4-8C49-CA1FAB6B9DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CarSales" sheetId="2" r:id="rId1"/>
@@ -20,10 +20,11 @@
     <sheet name="Sheet4" sheetId="6" r:id="rId5"/>
     <sheet name="Sheet5" sheetId="7" r:id="rId6"/>
     <sheet name="Sheet6" sheetId="8" r:id="rId7"/>
+    <sheet name="experimentation" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -6456,6 +6457,12 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>. Select the complete data column - Ctrl + Space</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
             <a:t>. Selecting multiple rows/columns using mouse - Click on the row/column index and then drag while pressing the mouse button</a:t>
           </a:r>
         </a:p>
@@ -7177,6 +7184,147 @@
             </a:rPr>
             <a:t>WHAT IF ANALYSIS</a:t>
           </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21421162-5138-77BA-9FB2-9B64F06B28C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="175260"/>
+          <a:ext cx="12184380" cy="3657600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>Selecting the data in excel:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100"/>
+            <a:t>Data</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t> Selection in Excel can be done using 3 methods:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>Shift + Arrows Keys - 4 </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>Shift + Space - 1 </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>Ctrl + Space - 1 </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>Ctrl + Shift + Arrow Keys - 4 </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>Ctrl + Shift + Space - 1</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>Ctrl + Shift + End - 1</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>Ctrl + Shift + Home - 1</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" baseline="0"/>
+            <a:t>Ctrl + A - 1</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -47900,4 +48048,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7593DD1-789D-40DE-ABE8-DCB81CB1145B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Automobile_Sector_Projects/Car_Sales_Analysis/CarSalesByModelEnd.xlsx
+++ b/Automobile_Sector_Projects/Car_Sales_Analysis/CarSalesByModelEnd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Automobile_Sector_Projects\Car_Sales_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73755A83-CAE4-41A4-8C49-CA1FAB6B9DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63EA74F-C5F2-4F4D-B5F0-43E3B1A8A358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Automobile_Sector_Projects/Car_Sales_Analysis/CarSalesByModelEnd.xlsx
+++ b/Automobile_Sector_Projects/Car_Sales_Analysis/CarSalesByModelEnd.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Automobile_Sector_Projects\Car_Sales_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63EA74F-C5F2-4F4D-B5F0-43E3B1A8A358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB79FDF-8DAC-4AC6-A7E9-12CD7398A2BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7281,13 +7281,13 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>Shift + Space - 1 </a:t>
+            <a:t>Shift + Space - 1 row</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>Ctrl + Space - 1 </a:t>
+            <a:t>Ctrl + Space - 1 column</a:t>
           </a:r>
         </a:p>
         <a:p>

--- a/Automobile_Sector_Projects/Car_Sales_Analysis/CarSalesByModelEnd.xlsx
+++ b/Automobile_Sector_Projects/Car_Sales_Analysis/CarSalesByModelEnd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Automobile_Sector_Projects\Car_Sales_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB79FDF-8DAC-4AC6-A7E9-12CD7398A2BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E4F411-3425-4A3D-AF8B-75463CCE146B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CarSales" sheetId="2" r:id="rId1"/>
@@ -6799,7 +6799,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>. VLOOKUP - vertical Lookup - has 4 parameters - Lookup Value, Lookup Range, Lookup Column Index, Exactness - lookup column has to be the leftmost column</a:t>
+            <a:t>. VLOOKUP - vertical Lookup - has 4 parameters - Lookup Value, Lookup Range, Lookup Column Index, Exactness - lookup column has to be the leftmost column.</a:t>
           </a:r>
         </a:p>
         <a:p>
